--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-count-same.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/top-count-same.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB97E307-FE97-46B0-9A13-1D3BCE4F68B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FB7E0BC-7248-4B84-B1AE-B31B61C32E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{393D9D70-43B0-41D6-A2EB-0694A4595578}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{BFBA7EFA-DF62-45EA-ACAD-98188AA79B5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576862615744" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{A0FAED8F-E04E-40F9-8D75-D4C6E1E13F35}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.57942534722" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{C56F5E06-9D7F-4E20-8722-F8BE1F49FA5C}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B4" sheet="Source"/>
   </cacheSource>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DB2FD364-EDDD-4639-9684-A6C95BB98058}" name="AllErrorPivot" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57EBFD0B-F7E6-40A9-AECF-FB3DCB054ECF}" name="AllErrorPivot" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -537,7 +537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{759ECFAF-44AC-4329-9365-9F9606EB8026}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FCF691D-1DD0-4309-A3B5-7693E125D161}">
   <dimension ref="A4:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -591,7 +591,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AAE04BB-B49B-4B5A-AD08-2C5682C4C9D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C6ED8A3-8953-47D1-9270-0BFE491553DE}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
